--- a/Result/profitability/7803.xlsx
+++ b/Result/profitability/7803.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:AM12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1827,6 +1827,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7803</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>21</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-84</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-394.83%</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-84</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-84</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.57125</v>
+      </c>
+      <c r="N12" t="n">
+        <v>47.16375</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1794871794871795</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-11.59</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.2201747720364742</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.05747126436781613</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-11.48</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.2185417856462974</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK12" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
